--- a/Document/텍스트.xlsx
+++ b/Document/텍스트.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rizen\OneDrive\Work\unity\ProjectES\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D7B38D-EAB6-452F-A18C-6DD420C76582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E109833A-13E1-40FA-ACA4-64FDD8480D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4910" yWindow="1550" windowWidth="31610" windowHeight="18750" xr2:uid="{0BC0353D-A8D0-4494-B3BE-FFD32DE26ABF}"/>
   </bookViews>
@@ -125,19 +125,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[카드게임으로 내기를 하는 *1와 *2
-*1가 져서 심부름을 한다]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>병사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -166,11 +153,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이… 이것을 부디…
-*3 공에게 전해주게…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>나는… 틀렸어… 털썩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,15 +162,6 @@
   </si>
   <si>
     <t>(전령… 인가? 어디 보자…)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[*3 공에게</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*마을로 향하는 상단이 습격당했다.
-최근에 출몰하기 시작한 마물로 판명되는 *인 것으로 보인다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -197,23 +170,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>게다가, *마을이라면 이 근처고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(상당히 귀한 물건이 있을 수도…
 오늘은 운이 좋은걸)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[병사에게 상황을 듣는 *1
-건수를 잡았다]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[위험하다는 이유로 반대하는 *2
-그래도 인생을 필 기회일지도 몰라
-*마을로 출발]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -246,10 +204,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>설마… *까지 가자는 얘기는 아니지?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>응</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -267,11 +221,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*라면 우리들 힘을 합쳐도 손가락 하나 당해낼 수 없다고.
-혹시나 마주치기라도 하면……</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이 일대에서 벗어나지 않는 이유도
 그 때문이잖아?</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -306,7 +255,58 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[집 앞으로 나온 *1]</t>
+    <t>아스타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이나시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[카드게임으로 내기를 하는 아스타와 이나시
+아스타가 져서 심부름을 한다]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[집 앞으로 나온 아스타]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[병사에게 상황을 듣는 아스타
+건수를 잡았다]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이… 이것을 부디…
+베린 공에게 전해주게…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[베린 공에게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메르시 마을로 향하는 상단이 습격당했다.
+최근에 출몰하기 시작한 마물로 판명되는 액체 인간인 것으로 보인다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게다가, 메르시 마을이라면 이 근처고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[위험하다는 이유로 반대하는 이나시
+그래도 인생을 필 기회일지도 몰라
+메르시 마을로 출발]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설마… 메르시 마을까지 가자는 얘기는 아니지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>액체 인간이라면 우리들 힘을 합쳐도 손가락 하나 당해낼 수 없다고.
+혹시나 마주치기라도 하면……</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +682,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
@@ -697,7 +697,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="6" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>20</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="7" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>2</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="8" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="9" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>4</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>21</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="14" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="15" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -804,12 +804,12 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B18" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="20" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>10</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>11</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="24" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>17</v>
@@ -854,7 +854,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>18</v>
@@ -862,264 +862,264 @@
     </row>
     <row r="27" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="B27" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B37" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="51" x14ac:dyDescent="0.45">
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="B39" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="51" x14ac:dyDescent="0.45">
       <c r="B44" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="51" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="51" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
